--- a/artfynd/A 32959-2026 artfynd.xlsx
+++ b/artfynd/A 32959-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136426698</v>
       </c>
       <c r="B2" t="n">
-        <v>92097</v>
+        <v>92098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136426699</v>
       </c>
       <c r="B3" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136426685</v>
       </c>
       <c r="B4" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136426688</v>
       </c>
       <c r="B5" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136426692</v>
       </c>
       <c r="B6" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136426693</v>
       </c>
       <c r="B7" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136426701</v>
       </c>
       <c r="B8" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136426694</v>
       </c>
       <c r="B9" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136426687</v>
       </c>
       <c r="B10" t="n">
-        <v>99376</v>
+        <v>99377</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136426686</v>
       </c>
       <c r="B11" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136426690</v>
       </c>
       <c r="B12" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136426695</v>
       </c>
       <c r="B13" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136426696</v>
       </c>
       <c r="B14" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136426697</v>
       </c>
       <c r="B15" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136426713</v>
       </c>
       <c r="B16" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>136426691</v>
       </c>
       <c r="B17" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>136426680</v>
       </c>
       <c r="B18" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2601,7 +2601,7 @@
         <v>136426681</v>
       </c>
       <c r="B19" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>136426712</v>
       </c>
       <c r="B20" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>136426710</v>
       </c>
       <c r="B21" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
